--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$114</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4125" uniqueCount="536">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -720,6 +723,70 @@
     <t>PV1-10</t>
   </si>
   <si>
+    <t>Encounter.serviceType.id</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Encounter.priority</t>
   </si>
   <si>
@@ -739,6 +806,18 @@
   </si>
   <si>
     <t>PV2-25</t>
+  </si>
+  <si>
+    <t>Encounter.priority.id</t>
+  </si>
+  <si>
+    <t>Encounter.priority.extension</t>
+  </si>
+  <si>
+    <t>Encounter.priority.coding</t>
+  </si>
+  <si>
+    <t>Encounter.priority.text</t>
   </si>
   <si>
     <t>Encounter.subject</t>
@@ -748,7 +827,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-patient)
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-patient|Group)
 </t>
   </si>
   <si>
@@ -887,7 +966,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-practitioner|PractitionerRole|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-relatedperson)
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-practitioner|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-relatedperson|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-practitionerrole)
 </t>
   </si>
   <si>
@@ -952,6 +1031,65 @@
     <t>PV1-44, PV1-45</t>
   </si>
   <si>
+    <t>Encounter.period.id</t>
+  </si>
+  <si>
+    <t>Encounter.period.extension</t>
+  </si>
+  <si>
+    <t>Encounter.period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>Encounter.period.end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
     <t>Encounter.length</t>
   </si>
   <si>
@@ -1011,7 +1149,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
+    <t xml:space="preserve">Reference(Condition|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-observation|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-procedure|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1046,7 +1184,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1)
+    <t xml:space="preserve">Reference(Condition|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-procedure)
 </t>
   </si>
   <si>
@@ -1078,6 +1216,18 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
+  </si>
+  <si>
+    <t>Encounter.diagnosis.use.id</t>
+  </si>
+  <si>
+    <t>Encounter.diagnosis.use.extension</t>
+  </si>
+  <si>
+    <t>Encounter.diagnosis.use.coding</t>
+  </si>
+  <si>
+    <t>Encounter.diagnosis.use.text</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1156,130 +1306,194 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-location|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-organization)
+</t>
+  </si>
+  <si>
+    <t>The location/organization from which the patient came before admission</t>
+  </si>
+  <si>
+    <t>The location/organization from which the patient came before admission.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=ORG].role</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.admitSource</t>
+  </si>
+  <si>
+    <t>From where patient was admitted (physician referral, transfer)</t>
+  </si>
+  <si>
+    <t>From where patient was admitted (physician referral, transfer).</t>
+  </si>
+  <si>
+    <t>From where the patient was admitted.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
+  </si>
+  <si>
+    <t>.admissionReferralSourceCode</t>
+  </si>
+  <si>
+    <t>PV1-14</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.admitSource.id</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.admitSource.extension</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.admitSource.coding</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.admitSource.text</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.reAdmission</t>
+  </si>
+  <si>
+    <t>The type of hospital re-admission that has occurred (if any). If the value is absent, then this is not identified as a readmission</t>
+  </si>
+  <si>
+    <t>Whether this hospitalization is a readmission and why if known.</t>
+  </si>
+  <si>
+    <t>The reason for re-admission of this hospitalization encounter.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+  </si>
+  <si>
+    <t>PV1-13</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.reAdmission.id</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.reAdmission.extension</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.reAdmission.coding</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.reAdmission.text</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dietPreference</t>
+  </si>
+  <si>
+    <t>Diet preferences reported by the patient</t>
+  </si>
+  <si>
+    <t>Diet preferences reported by the patient.</t>
+  </si>
+  <si>
+    <t>For example, a patient may request both a dairy-free and nut-free diet preference (not mutually exclusive).</t>
+  </si>
+  <si>
+    <t>Used to track patient's diet restrictions and/or preference. For a complete description of the nutrition needs of a patient during their stay, one should use the nutritionOrder resource which links to Encounter.</t>
+  </si>
+  <si>
+    <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
+  </si>
+  <si>
+    <t>PV1-38</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dietPreference.id</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dietPreference.extension</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dietPreference.coding</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dietPreference.text</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialCourtesy</t>
+  </si>
+  <si>
+    <t>Special courtesies (VIP, board member)</t>
+  </si>
+  <si>
+    <t>Special courtesies (VIP, board member).</t>
+  </si>
+  <si>
+    <t>Special courtesies.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
+  </si>
+  <si>
+    <t>.specialCourtesiesCode</t>
+  </si>
+  <si>
+    <t>PV1-16</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialCourtesy.id</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialCourtesy.extension</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialCourtesy.coding</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialCourtesy.text</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialArrangement</t>
+  </si>
+  <si>
+    <t>Wheelchair, translator, stretcher, etc.</t>
+  </si>
+  <si>
+    <t>Any special requests that have been made for this hospitalization encounter, such as the provision of specific equipment or other things.</t>
+  </si>
+  <si>
+    <t>Special arrangements.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
+  </si>
+  <si>
+    <t>.specialArrangementCode</t>
+  </si>
+  <si>
+    <t>PV1-15 / OBR-30 / OBR-43</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialArrangement.id</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialArrangement.extension</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialArrangement.coding</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialArrangement.text</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.destination</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(Location|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
-    <t>The location/organization from which the patient came before admission</t>
-  </si>
-  <si>
-    <t>The location/organization from which the patient came before admission.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=ORG].role</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.admitSource</t>
-  </si>
-  <si>
-    <t>From where patient was admitted (physician referral, transfer)</t>
-  </si>
-  <si>
-    <t>From where patient was admitted (physician referral, transfer).</t>
-  </si>
-  <si>
-    <t>From where the patient was admitted.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
-  </si>
-  <si>
-    <t>.admissionReferralSourceCode</t>
-  </si>
-  <si>
-    <t>PV1-14</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.reAdmission</t>
-  </si>
-  <si>
-    <t>The type of hospital re-admission that has occurred (if any). If the value is absent, then this is not identified as a readmission</t>
-  </si>
-  <si>
-    <t>Whether this hospitalization is a readmission and why if known.</t>
-  </si>
-  <si>
-    <t>The reason for re-admission of this hospitalization encounter.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
-  </si>
-  <si>
-    <t>PV1-13</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dietPreference</t>
-  </si>
-  <si>
-    <t>Diet preferences reported by the patient</t>
-  </si>
-  <si>
-    <t>Diet preferences reported by the patient.</t>
-  </si>
-  <si>
-    <t>For example, a patient may request both a dairy-free and nut-free diet preference (not mutually exclusive).</t>
-  </si>
-  <si>
-    <t>Used to track patient's diet restrictions and/or preference. For a complete description of the nutrition needs of a patient during their stay, one should use the nutritionOrder resource which links to Encounter.</t>
-  </si>
-  <si>
-    <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
-  </si>
-  <si>
-    <t>PV1-38</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.specialCourtesy</t>
-  </si>
-  <si>
-    <t>Special courtesies (VIP, board member)</t>
-  </si>
-  <si>
-    <t>Special courtesies (VIP, board member).</t>
-  </si>
-  <si>
-    <t>Special courtesies.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
-  </si>
-  <si>
-    <t>.specialCourtesiesCode</t>
-  </si>
-  <si>
-    <t>PV1-16</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.specialArrangement</t>
-  </si>
-  <si>
-    <t>Wheelchair, translator, stretcher, etc.</t>
-  </si>
-  <si>
-    <t>Any special requests that have been made for this hospitalization encounter, such as the provision of specific equipment or other things.</t>
-  </si>
-  <si>
-    <t>Special arrangements.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
-  </si>
-  <si>
-    <t>.specialArrangementCode</t>
-  </si>
-  <si>
-    <t>PV1-15 / OBR-30 / OBR-43</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.destination</t>
-  </si>
-  <si>
     <t>Location/organization to which the patient is discharged</t>
   </si>
   <si>
@@ -1340,7 +1554,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-location)
 </t>
   </si>
   <si>
@@ -1399,6 +1613,18 @@
     <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
+    <t>Encounter.location.physicalType.id</t>
+  </si>
+  <si>
+    <t>Encounter.location.physicalType.extension</t>
+  </si>
+  <si>
+    <t>Encounter.location.physicalType.coding</t>
+  </si>
+  <si>
+    <t>Encounter.location.physicalType.text</t>
+  </si>
+  <si>
     <t>Encounter.location.period</t>
   </si>
   <si>
@@ -1411,7 +1637,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-organization)
 </t>
   </si>
   <si>
@@ -1577,6 +1803,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1750,11 +1991,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN74"/>
+  <dimension ref="A1:AN114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.16015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.16015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.46875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.46875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1763,7 +2004,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="135.7421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="181.2734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1781,7 +2022,7 @@
     <col min="26" max="26" width="52.75390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="39.16015625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1916,7 +2157,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2028,7 +2269,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -2142,7 +2383,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -2254,7 +2495,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2368,7 +2609,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2482,7 +2723,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2596,7 +2837,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2710,7 +2951,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2824,7 +3065,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2959,7 +3200,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>80</v>
@@ -3071,7 +3312,7 @@
         <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>89</v>
@@ -3166,7 +3407,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>164</v>
       </c>
@@ -3280,7 +3521,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>170</v>
       </c>
@@ -3392,7 +3633,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>175</v>
       </c>
@@ -3506,7 +3747,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>178</v>
       </c>
@@ -3622,7 +3863,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>183</v>
       </c>
@@ -3734,7 +3975,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>184</v>
       </c>
@@ -3865,7 +4106,7 @@
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -3958,7 +4199,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>198</v>
       </c>
@@ -4070,7 +4311,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>201</v>
       </c>
@@ -4182,7 +4423,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>202</v>
       </c>
@@ -4296,7 +4537,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>203</v>
       </c>
@@ -4412,7 +4653,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>204</v>
       </c>
@@ -4524,7 +4765,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>207</v>
       </c>
@@ -4655,7 +4896,7 @@
         <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>80</v>
@@ -4769,7 +5010,7 @@
         <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
@@ -4862,7 +5103,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>227</v>
       </c>
@@ -4890,13 +5131,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4923,13 +5164,13 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>229</v>
+        <v>80</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -4947,7 +5188,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4959,38 +5200,38 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>231</v>
+        <v>169</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>235</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -4999,19 +5240,19 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>236</v>
+        <v>134</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>237</v>
+        <v>135</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>238</v>
+        <v>176</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>239</v>
+        <v>137</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5049,51 +5290,51 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>241</v>
+        <v>169</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>242</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5107,7 +5348,7 @@
         <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>80</v>
@@ -5116,16 +5357,20 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5173,7 +5418,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5188,56 +5433,60 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>253</v>
+        <v>171</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5285,13 +5534,13 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
@@ -5300,24 +5549,24 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5328,25 +5577,25 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5373,13 +5622,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5397,13 +5646,13 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>80</v>
@@ -5412,24 +5661,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>80</v>
+        <v>253</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5536,12 +5785,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5611,16 +5860,16 @@
         <v>80</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>177</v>
@@ -5652,14 +5901,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5669,28 +5918,28 @@
         <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>180</v>
+        <v>233</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>181</v>
+        <v>234</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>143</v>
+        <v>236</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5739,7 +5988,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5751,27 +6000,27 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>131</v>
+        <v>238</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5782,10 +6031,10 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
@@ -5794,18 +6043,20 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5829,13 +6080,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5853,13 +6104,13 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
@@ -5868,55 +6119,57 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>274</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>185</v>
+        <v>261</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -5965,7 +6218,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5980,24 +6233,24 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6008,7 +6261,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -6020,13 +6273,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6077,13 +6330,13 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
@@ -6092,28 +6345,28 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>80</v>
+        <v>277</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6129,16 +6382,16 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6189,7 +6442,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6204,24 +6457,24 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6232,29 +6485,27 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6303,13 +6554,13 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
@@ -6318,24 +6569,24 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6358,17 +6609,15 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>303</v>
+        <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>304</v>
+        <v>172</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6417,7 +6666,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>302</v>
+        <v>174</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6429,31 +6678,31 @@
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>298</v>
+        <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>307</v>
+        <v>169</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>308</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6469,19 +6718,19 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>135</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>176</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>313</v>
+        <v>137</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6507,13 +6756,13 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>314</v>
+        <v>80</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -6531,7 +6780,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6543,31 +6792,31 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>317</v>
+        <v>169</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>319</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>310</v>
+        <v>179</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6580,24 +6829,26 @@
         <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>321</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>322</v>
+        <v>180</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6645,7 +6896,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>182</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6657,27 +6908,27 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>317</v>
+        <v>131</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>319</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6691,7 +6942,7 @@
         <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>80</v>
@@ -6700,15 +6951,17 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6733,13 +6986,13 @@
         <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -6757,7 +7010,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6772,24 +7025,24 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6812,13 +7065,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>172</v>
+        <v>301</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>173</v>
+        <v>302</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6869,7 +7122,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>174</v>
+        <v>300</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6881,38 +7134,38 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>169</v>
+        <v>303</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -6921,20 +7174,18 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>135</v>
+        <v>307</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -6983,43 +7234,43 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>177</v>
+        <v>305</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>169</v>
+        <v>310</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>80</v>
+        <v>311</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7032,26 +7283,22 @@
         <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>314</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>180</v>
+        <v>315</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7099,7 +7346,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>182</v>
+        <v>313</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7111,59 +7358,59 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>131</v>
+        <v>317</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>80</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>332</v>
+        <v>185</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7213,10 +7460,10 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>88</v>
@@ -7228,24 +7475,24 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>337</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7268,13 +7515,13 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>339</v>
+        <v>172</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>340</v>
+        <v>173</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7301,13 +7548,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>341</v>
+        <v>80</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7325,7 +7572,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>338</v>
+        <v>174</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7337,7 +7584,7 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
@@ -7352,23 +7599,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -7380,15 +7627,17 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>344</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>345</v>
+        <v>135</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7425,37 +7674,37 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>343</v>
+        <v>177</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>347</v>
+        <v>169</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
@@ -7466,10 +7715,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7480,28 +7729,28 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7551,16 +7800,16 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>100</v>
@@ -7569,21 +7818,21 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7603,25 +7852,27 @@
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="R52" t="s" s="2">
         <v>80</v>
       </c>
@@ -7665,7 +7916,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7674,7 +7925,7 @@
         <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>100</v>
@@ -7683,21 +7934,21 @@
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>80</v>
+        <v>345</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7720,15 +7971,17 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>171</v>
+        <v>347</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>172</v>
+        <v>348</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -7777,7 +8030,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7789,31 +8042,31 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>169</v>
+        <v>351</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>133</v>
+        <v>354</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7823,25 +8076,25 @@
         <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>135</v>
+        <v>355</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>176</v>
+        <v>356</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>137</v>
+        <v>357</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7867,13 +8120,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -7891,7 +8144,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>177</v>
+        <v>353</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7903,31 +8156,31 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>169</v>
+        <v>361</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>80</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>179</v>
+        <v>354</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7937,29 +8190,27 @@
         <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>365</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>180</v>
+        <v>366</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>181</v>
+        <v>356</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8007,7 +8258,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>182</v>
+        <v>364</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8019,27 +8270,27 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>131</v>
+        <v>361</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>80</v>
+        <v>363</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8050,7 +8301,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
@@ -8059,16 +8310,16 @@
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8119,13 +8370,13 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
@@ -8137,21 +8388,21 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>150</v>
+        <v>370</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>365</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8174,13 +8425,13 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>367</v>
+        <v>171</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>368</v>
+        <v>172</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>369</v>
+        <v>173</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8231,7 +8482,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>366</v>
+        <v>174</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8243,13 +8494,13 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>370</v>
+        <v>169</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
@@ -8258,23 +8509,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -8286,15 +8537,17 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>372</v>
+        <v>135</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8319,13 +8572,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>375</v>
+        <v>80</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8343,71 +8596,75 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>371</v>
+        <v>177</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>376</v>
+        <v>169</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>377</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>180</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8431,13 +8688,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -8455,50 +8712,50 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>378</v>
+        <v>182</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>80</v>
+        <v>375</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -8507,23 +8764,21 @@
         <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>211</v>
+        <v>376</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8547,13 +8802,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>389</v>
+        <v>80</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -8571,13 +8826,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -8586,24 +8841,24 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>392</v>
+        <v>381</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8614,10 +8869,10 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>80</v>
@@ -8629,10 +8884,10 @@
         <v>211</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8662,10 +8917,10 @@
         <v>112</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -8683,13 +8938,13 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
@@ -8701,21 +8956,21 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>398</v>
+        <v>169</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>399</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8726,7 +8981,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>80</v>
@@ -8738,13 +8993,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>401</v>
+        <v>172</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>402</v>
+        <v>173</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8771,13 +9026,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>403</v>
+        <v>80</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -8795,50 +9050,50 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>400</v>
+        <v>174</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>405</v>
+        <v>169</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>406</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>80</v>
@@ -8850,15 +9105,17 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>367</v>
+        <v>134</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>408</v>
+        <v>135</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -8895,51 +9152,51 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>177</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>410</v>
+        <v>169</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8950,28 +9207,32 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>413</v>
+        <v>233</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -8995,13 +9256,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>416</v>
+        <v>80</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9019,13 +9280,13 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>237</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
@@ -9037,21 +9298,21 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>417</v>
+        <v>238</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>418</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>390</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>419</v>
+        <v>390</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9062,30 +9323,32 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>420</v>
+        <v>241</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>421</v>
+        <v>242</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
@@ -9133,13 +9396,13 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>419</v>
+        <v>245</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
@@ -9151,21 +9414,21 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>423</v>
+        <v>246</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9188,13 +9451,13 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>171</v>
+        <v>392</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>172</v>
+        <v>393</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>173</v>
+        <v>394</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9245,7 +9508,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>174</v>
+        <v>391</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9257,13 +9520,13 @@
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>169</v>
+        <v>395</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -9272,16 +9535,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>425</v>
+        <v>396</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>425</v>
+        <v>396</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9300,16 +9563,16 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>397</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>135</v>
+        <v>398</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>176</v>
+        <v>399</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>137</v>
+        <v>400</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9359,7 +9622,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>177</v>
+        <v>396</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9371,13 +9634,13 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>169</v>
+        <v>401</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
@@ -9388,46 +9651,44 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>180</v>
+        <v>403</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>181</v>
+        <v>404</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
@@ -9475,25 +9736,25 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>182</v>
+        <v>402</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>131</v>
+        <v>406</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
@@ -9502,12 +9763,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9515,7 +9776,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>88</v>
@@ -9530,13 +9791,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>428</v>
+        <v>171</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>429</v>
+        <v>172</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>430</v>
+        <v>173</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9587,10 +9848,10 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>427</v>
+        <v>174</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>88</v>
@@ -9599,38 +9860,38 @@
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>431</v>
+        <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>432</v>
+        <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>80</v>
@@ -9642,16 +9903,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>435</v>
+        <v>135</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>436</v>
+        <v>176</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>437</v>
+        <v>137</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9677,13 +9938,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>439</v>
+        <v>80</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -9701,25 +9962,25 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>434</v>
+        <v>177</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>440</v>
+        <v>169</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -9728,46 +9989,48 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>442</v>
+        <v>180</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>443</v>
+        <v>181</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
       </c>
@@ -9791,13 +10054,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>445</v>
+        <v>80</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>446</v>
+        <v>80</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -9815,25 +10078,25 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>441</v>
+        <v>182</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
@@ -9842,12 +10105,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9870,13 +10133,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>448</v>
+        <v>411</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>449</v>
+        <v>412</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9927,7 +10190,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9945,21 +10208,21 @@
         <v>80</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>278</v>
+        <v>150</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>80</v>
+        <v>413</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9973,7 +10236,7 @@
         <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>80</v>
@@ -9982,13 +10245,13 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>451</v>
+        <v>415</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>453</v>
+        <v>417</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10039,7 +10302,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10054,24 +10317,24 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>454</v>
+        <v>418</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10085,7 +10348,7 @@
         <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>80</v>
@@ -10094,17 +10357,15 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>457</v>
+        <v>211</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10129,13 +10390,13 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>80</v>
+        <v>423</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -10153,7 +10414,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10168,19 +10429,4595 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="B91" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN74" t="s" s="2">
+      <c r="B92" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN114">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI113">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-encounter.xlsx
+++ b/dev/StructureDefinition-ph-core-encounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
